--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_150_R15.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_150_R15.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.6781</v>
+        <v>3.2672</v>
       </c>
       <c r="E2" t="n">
-        <v>2.9445</v>
+        <v>3.2983</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2664</v>
+        <v>-0.0311</v>
       </c>
       <c r="G2" t="n">
         <v>2.931</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.0029</v>
+        <v>-0.4138</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7468</v>
+        <v>-0.393</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2561</v>
+        <v>-0.0209</v>
       </c>
       <c r="V2" t="n">
         <v>1.214</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>D. ALSTON JR.</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8592</v>
+        <v>1.8428</v>
       </c>
       <c r="E3" t="n">
-        <v>2.55</v>
+        <v>2.8179</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6909</v>
+        <v>-0.9751</v>
       </c>
       <c r="G3" t="n">
-        <v>0.3646</v>
+        <v>-0.1597</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.221</v>
+        <v>-1.294</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5856</v>
+        <v>1.1343</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3774</v>
+        <v>1.5385</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0524</v>
+        <v>-0.1779</v>
       </c>
       <c r="L3" t="n">
-        <v>1.325</v>
+        <v>1.7164</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0127</v>
+        <v>-1.6982</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2734</v>
+        <v>-1.1161</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.5821</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3917</v>
+        <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>3.8346</v>
+        <v>0.5386</v>
       </c>
       <c r="T3" t="n">
-        <v>3.9045</v>
+        <v>0.7433</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0698</v>
+        <v>-0.2047</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2525</v>
+        <v>0.5361</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.2525</v>
+        <v>0.5361</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.4165</v>
+        <v>1.7943</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0074</v>
+        <v>0.3179</v>
       </c>
       <c r="F4" t="n">
-        <v>1.4091</v>
+        <v>1.4763</v>
       </c>
       <c r="G4" t="n">
         <v>0.8306</v>
@@ -766,13 +766,13 @@
         <v>1.3917</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2697</v>
+        <v>0.1081</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4481</v>
+        <v>-0.1375</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1784</v>
+        <v>0.2456</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5361</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. NIANG</t>
+          <t>A. DIARRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3381</v>
+        <v>1.3136</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8894</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2275</v>
+        <v>1.9432</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8716</v>
+        <v>2.3201</v>
       </c>
       <c r="H5" t="n">
-        <v>1.8343</v>
+        <v>1.4969</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0373</v>
+        <v>0.8231000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>2.5503</v>
+        <v>1.9022</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4031</v>
+        <v>1.8654</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1472</v>
+        <v>0.0368</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3213</v>
+        <v>0.4179</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5688</v>
+        <v>-0.3684</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8901</v>
+        <v>0.7863</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.6237</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.4793</v>
+        <v>-2.3195</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>0.232</v>
+        <v>-0.0786</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0395</v>
+        <v>-0.2122</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1924</v>
+        <v>0.1336</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. ALSTON JR.</t>
+          <t>S. NIANG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2963</v>
+        <v>1.1769</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2714</v>
+        <v>-1.0506</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9751</v>
+        <v>2.2275</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.1597</v>
+        <v>2.8716</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.294</v>
+        <v>1.8343</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1343</v>
+        <v>1.0373</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5385</v>
+        <v>2.5503</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.1779</v>
+        <v>2.4031</v>
       </c>
       <c r="L6" t="n">
-        <v>1.7164</v>
+        <v>0.1472</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.6982</v>
+        <v>0.3213</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1161</v>
+        <v>-0.5688</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5821</v>
+        <v>0.8901</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0707</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1968</v>
+        <v>-0.1217</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2047</v>
+        <v>0.1924</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5361</v>
+        <v>-0.1418</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DIARRA</t>
+          <t>L. VILDOZA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0777</v>
+        <v>0.2647</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8653999999999999</v>
+        <v>1.3152</v>
       </c>
       <c r="F7" t="n">
-        <v>1.9432</v>
+        <v>-1.0505</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3201</v>
+        <v>1.3761</v>
       </c>
       <c r="H7" t="n">
-        <v>1.4969</v>
+        <v>-1.5448</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8231000000000001</v>
+        <v>2.9209</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9022</v>
+        <v>4.4718</v>
       </c>
       <c r="K7" t="n">
-        <v>1.8654</v>
+        <v>0.39</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0368</v>
+        <v>4.0818</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4179</v>
+        <v>-3.0957</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3684</v>
+        <v>-1.9348</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7863</v>
+        <v>-1.1609</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.9278</v>
+        <v>-2.0876</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3195</v>
+        <v>-3.4793</v>
       </c>
       <c r="R7" t="n">
         <v>1.3917</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3145</v>
+        <v>0.5819</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4481</v>
+        <v>0.3227</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1336</v>
+        <v>0.2592</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L. VILDOZA</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,40 +1033,40 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8864</v>
+        <v>-0.5453</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0296</v>
+        <v>0.1792</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9161</v>
+        <v>-0.7245</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3761</v>
+        <v>0.3646</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.5448</v>
+        <v>-0.221</v>
       </c>
       <c r="I8" t="n">
-        <v>2.9209</v>
+        <v>0.5856</v>
       </c>
       <c r="J8" t="n">
-        <v>4.4718</v>
+        <v>2.3774</v>
       </c>
       <c r="K8" t="n">
-        <v>0.39</v>
+        <v>1.0524</v>
       </c>
       <c r="L8" t="n">
-        <v>4.0818</v>
+        <v>1.325</v>
       </c>
       <c r="M8" t="n">
-        <v>-3.0957</v>
+        <v>-2.0127</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.9348</v>
+        <v>-1.2734</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1609</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P8" t="n">
         <v>-2.0876</v>
@@ -1078,22 +1078,22 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5693</v>
+        <v>1.4301</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.963</v>
+        <v>1.5336</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3936</v>
+        <v>-0.1034</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3943</v>
+        <v>-0.2525</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.2525</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.976</v>
+        <v>-1.2943</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4974</v>
+        <v>-3.1436</v>
       </c>
       <c r="F9" t="n">
-        <v>2.5215</v>
+        <v>1.8493</v>
       </c>
       <c r="G9" t="n">
         <v>0.2341</v>
@@ -1156,13 +1156,13 @@
         <v>1.8556</v>
       </c>
       <c r="S9" t="n">
-        <v>0.326</v>
+        <v>0.0077</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5975</v>
+        <v>-0.2436</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9234</v>
+        <v>0.2513</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9475</v>
+        <v>-1.8735</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9855</v>
+        <v>-1.1467</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9621</v>
+        <v>-0.7268</v>
       </c>
       <c r="G10" t="n">
         <v>-2.6822</v>
@@ -1234,13 +1234,13 @@
         <v>0.6959</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1805</v>
+        <v>0.2546</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2636</v>
+        <v>0.1024</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.083</v>
+        <v>0.1522</v>
       </c>
       <c r="V10" t="n">
         <v>-0.1418</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.7868</v>
+        <v>-2.0819</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1677</v>
+        <v>-0.6645</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6191</v>
+        <v>-1.4174</v>
       </c>
       <c r="G11" t="n">
         <v>-2.5715</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0167</v>
+        <v>0.7215</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1221</v>
+        <v>0.6253</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1054</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-9.228899999999999</v>
+        <v>-8.9041</v>
       </c>
       <c r="E12" t="n">
-        <v>-8.1182</v>
+        <v>-7.8941</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1108</v>
+        <v>-1.0099</v>
       </c>
       <c r="G12" t="n">
         <v>-9.021100000000001</v>
@@ -1390,13 +1390,13 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>0.72</v>
+        <v>1.0449</v>
       </c>
       <c r="T12" t="n">
-        <v>0.6844</v>
+        <v>0.9085</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0356</v>
+        <v>0.1364</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.159699999999999</v>
+        <v>-5.039599999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-7.720699999999999</v>
+        <v>-6.600500000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>1.560800000000001</v>
+        <v>1.561000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-3.506400000000001</v>
@@ -1447,7 +1447,7 @@
         <v>2.488999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>6.088400000000002</v>
+        <v>6.0884</v>
       </c>
       <c r="M13" t="n">
         <v>-12.0839</v>
@@ -1459,7 +1459,7 @@
         <v>-2.9269</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.7989</v>
+        <v>-5.798900000000001</v>
       </c>
       <c r="Q13" t="n">
         <v>-20.8757</v>
@@ -1468,13 +1468,13 @@
         <v>15.0768</v>
       </c>
       <c r="S13" t="n">
-        <v>3.1455</v>
+        <v>4.2657</v>
       </c>
       <c r="T13" t="n">
-        <v>2.007400000000001</v>
+        <v>3.1278</v>
       </c>
       <c r="U13" t="n">
-        <v>1.138</v>
+        <v>1.1379</v>
       </c>
       <c r="V13" t="n">
         <v>-8.326672684688674e-17</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>E. BRYANT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.9125</v>
+        <v>4.0394</v>
       </c>
       <c r="E14" t="n">
-        <v>4.8968</v>
+        <v>1.4423</v>
       </c>
       <c r="F14" t="n">
-        <v>1.0157</v>
+        <v>2.5971</v>
       </c>
       <c r="G14" t="n">
-        <v>3.5877</v>
+        <v>0.9808</v>
       </c>
       <c r="H14" t="n">
-        <v>5.2806</v>
+        <v>2.2756</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.6929</v>
+        <v>-1.2948</v>
       </c>
       <c r="J14" t="n">
-        <v>5.353</v>
+        <v>1.8241</v>
       </c>
       <c r="K14" t="n">
-        <v>5.0954</v>
+        <v>2.2693</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2576</v>
+        <v>-0.4452</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.7654</v>
+        <v>-0.8433</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1852</v>
+        <v>0.0063</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.9505</v>
+        <v>-0.8497</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.3917</v>
+        <v>2.3195</v>
       </c>
       <c r="Q14" t="n">
-        <v>-4.639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R14" t="n">
-        <v>3.2473</v>
+        <v>3.4793</v>
       </c>
       <c r="S14" t="n">
-        <v>3.0386</v>
+        <v>-0.4749</v>
       </c>
       <c r="T14" t="n">
-        <v>2.9688</v>
+        <v>-0.436</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0699</v>
+        <v>-0.0389</v>
       </c>
       <c r="V14" t="n">
-        <v>0.6778999999999999</v>
+        <v>1.214</v>
       </c>
       <c r="W14" t="n">
         <v>1.214</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. BRYANT</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4262</v>
+        <v>3.2738</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6167</v>
+        <v>2.5377</v>
       </c>
       <c r="F15" t="n">
-        <v>2.8095</v>
+        <v>0.7361</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9808</v>
+        <v>3.5877</v>
       </c>
       <c r="H15" t="n">
-        <v>2.2756</v>
+        <v>5.2806</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.2948</v>
+        <v>-1.6929</v>
       </c>
       <c r="J15" t="n">
-        <v>1.8241</v>
+        <v>5.353</v>
       </c>
       <c r="K15" t="n">
-        <v>2.2693</v>
+        <v>5.0954</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.4452</v>
+        <v>0.2576</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.8433</v>
+        <v>-1.7654</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0063</v>
+        <v>0.1852</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.8497</v>
+        <v>-1.9505</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3195</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1598</v>
+        <v>-4.639</v>
       </c>
       <c r="R15" t="n">
-        <v>3.4793</v>
+        <v>3.2473</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0881</v>
+        <v>0.4</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.2617</v>
+        <v>0.6097</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1735</v>
+        <v>-0.2098</v>
       </c>
       <c r="V15" t="n">
-        <v>1.214</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W15" t="n">
         <v>1.214</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3297</v>
+        <v>1.8745</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3252</v>
+        <v>0.679</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0046</v>
+        <v>1.1954</v>
       </c>
       <c r="G16" t="n">
         <v>3.0373</v>
@@ -1702,13 +1702,13 @@
         <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4756</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8962</v>
+        <v>-0.5423</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5794</v>
+        <v>-0.3886</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. JONES</t>
+          <t>C. MALCOLM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9657</v>
+        <v>1.3586</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3353</v>
+        <v>1.6568</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3696</v>
+        <v>-0.2982</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0863</v>
+        <v>0.5516</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7204</v>
+        <v>1.5787</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8067</v>
+        <v>-1.0271</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2983</v>
+        <v>2.1991</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6456</v>
+        <v>1.6973</v>
       </c>
       <c r="L17" t="n">
-        <v>1.6527</v>
+        <v>0.5018</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.212</v>
+        <v>-1.6476</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.366</v>
+        <v>-0.1186</v>
       </c>
       <c r="O17" t="n">
-        <v>0.154</v>
+        <v>-1.529</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1656</v>
+        <v>-1.2109</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1968</v>
+        <v>-0.5423</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0312</v>
+        <v>-0.6686</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.214</v>
+        <v>0.3943</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.214</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. MALCOLM</t>
+          <t>C. JONES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7131</v>
+        <v>1.0666</v>
       </c>
       <c r="E18" t="n">
-        <v>1.303</v>
+        <v>1.3353</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5899</v>
+        <v>-0.2688</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5516</v>
+        <v>1.0863</v>
       </c>
       <c r="H18" t="n">
-        <v>1.5787</v>
+        <v>-0.7204</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0271</v>
+        <v>1.8067</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1991</v>
+        <v>2.2983</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6973</v>
+        <v>0.6456</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5018</v>
+        <v>1.6527</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6476</v>
+        <v>-1.212</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1186</v>
+        <v>-1.366</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.529</v>
+        <v>0.154</v>
       </c>
       <c r="P18" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.8565</v>
+        <v>0.2664</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8962</v>
+        <v>0.1968</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.9603</v>
+        <v>0.0696</v>
       </c>
       <c r="V18" t="n">
-        <v>0.3943</v>
+        <v>-1.214</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3943</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2044</v>
+        <v>0.8778</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5069</v>
+        <v>-2.0351</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7112</v>
+        <v>2.9129</v>
       </c>
       <c r="G19" t="n">
         <v>-0.8658</v>
@@ -1936,13 +1936,13 @@
         <v>3.0154</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7855</v>
+        <v>-0.112</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7389</v>
+        <v>-0.2671</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0466</v>
+        <v>0.1551</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Y. MADAR</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3365</v>
+        <v>-0.2241</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8643</v>
+        <v>-1.317</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4722</v>
+        <v>1.093</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2618</v>
+        <v>-2.4178</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6399</v>
+        <v>-0.1126</v>
       </c>
       <c r="I20" t="n">
-        <v>0.3781</v>
+        <v>-2.3053</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7149</v>
+        <v>-0.999</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3038</v>
+        <v>0.3529</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5889</v>
+        <v>-1.3519</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5469000000000001</v>
+        <v>-1.4189</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3361</v>
+        <v>-0.4655</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.2108</v>
+        <v>-0.9534</v>
       </c>
       <c r="P20" t="n">
-        <v>0.232</v>
+        <v>3.7112</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.232</v>
+        <v>3.7112</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3066</v>
+        <v>-0.4452</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1494</v>
+        <v>-0.3181</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1573</v>
+        <v>-0.1272</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>Y. MADAR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5602</v>
+        <v>-1.1006</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2606</v>
+        <v>-0.6284</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7004</v>
+        <v>-0.4722</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4178</v>
+        <v>-1.2618</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1126</v>
+        <v>-1.6399</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3053</v>
+        <v>0.3781</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.999</v>
+        <v>-0.7149</v>
       </c>
       <c r="K21" t="n">
-        <v>0.3529</v>
+        <v>-1.3038</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3519</v>
+        <v>0.5889</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4189</v>
+        <v>-0.5469000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4655</v>
+        <v>-0.3361</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9534</v>
+        <v>-0.2108</v>
       </c>
       <c r="P21" t="n">
-        <v>3.7112</v>
+        <v>0.232</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>3.7112</v>
+        <v>0.232</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7814</v>
+        <v>-0.0707</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2617</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5197000000000001</v>
+        <v>-0.1573</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4951</v>
+        <v>-4.22</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.406</v>
+        <v>-5.2317</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9109</v>
+        <v>1.0117</v>
       </c>
       <c r="G22" t="n">
         <v>-1.1919</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.2192</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9006</v>
+        <v>0.07489999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0435</v>
+        <v>0.1443</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>6.1598</v>
+        <v>6.946000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.5608</v>
+        <v>-1.561100000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>7.720599999999999</v>
+        <v>8.507</v>
       </c>
       <c r="G23" t="n">
-        <v>3.5064</v>
+        <v>3.506400000000001</v>
       </c>
       <c r="H23" t="n">
         <v>6.668</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.1617</v>
+        <v>-3.161700000000001</v>
       </c>
       <c r="J23" t="n">
         <v>12.0838</v>
@@ -2248,16 +2248,16 @@
         <v>20.8758</v>
       </c>
       <c r="S23" t="n">
-        <v>-3.1454</v>
+        <v>-2.359</v>
       </c>
       <c r="T23" t="n">
         <v>-1.1379</v>
       </c>
       <c r="U23" t="n">
-        <v>-2.0076</v>
+        <v>-1.2214</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.110223024625157e-16</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>2.5698</v>
